--- a/artfynd/A 52471-2025 artfynd.xlsx
+++ b/artfynd/A 52471-2025 artfynd.xlsx
@@ -11099,7 +11099,7 @@
         <v>130063333</v>
       </c>
       <c r="B93" t="n">
-        <v>5179</v>
+        <v>5182</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11221,7 +11221,7 @@
         <v>130063340</v>
       </c>
       <c r="B94" t="n">
-        <v>5179</v>
+        <v>5182</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11324,7 +11324,7 @@
         <v>130063342</v>
       </c>
       <c r="B95" t="n">
-        <v>5179</v>
+        <v>5182</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>

--- a/artfynd/A 52471-2025 artfynd.xlsx
+++ b/artfynd/A 52471-2025 artfynd.xlsx
@@ -11125,11 +11125,7 @@
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
-      <c r="M93" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
           <t>Norra Rävmarken, Dls</t>
@@ -11350,11 +11346,7 @@
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
-      <c r="M95" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
           <t>Norra Rävmarken, Dls</t>

--- a/artfynd/A 52471-2025 artfynd.xlsx
+++ b/artfynd/A 52471-2025 artfynd.xlsx
@@ -11099,7 +11099,7 @@
         <v>130063333</v>
       </c>
       <c r="B93" t="n">
-        <v>5182</v>
+        <v>5188</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -11217,7 +11217,7 @@
         <v>130063340</v>
       </c>
       <c r="B94" t="n">
-        <v>5182</v>
+        <v>5188</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11320,7 +11320,7 @@
         <v>130063342</v>
       </c>
       <c r="B95" t="n">
-        <v>5182</v>
+        <v>5188</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
